--- a/samples/Trial_Balance_IN_Jul-26.xlsx
+++ b/samples/Trial_Balance_IN_Jul-26.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D44"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>14466119.8</v>
+        <v>261463736.49</v>
       </c>
     </row>
     <row r="8">
@@ -464,7 +464,7 @@
         <v>Cash</v>
       </c>
       <c r="D8">
-        <v>29108.1</v>
+        <v>82450</v>
       </c>
     </row>
     <row r="9">
@@ -478,7 +478,7 @@
         <v>Accounts Receivable</v>
       </c>
       <c r="D9">
-        <v>9837027.2</v>
+        <v>138370500</v>
       </c>
     </row>
     <row r="10">
@@ -492,7 +492,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D10">
-        <v>657667.1</v>
+        <v>6227400</v>
       </c>
     </row>
     <row r="11">
@@ -506,7 +506,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D11">
-        <v>516658.4</v>
+        <v>5024600</v>
       </c>
     </row>
     <row r="12">
@@ -520,7 +520,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D12">
-        <v>1209517.5</v>
+        <v>11979500</v>
       </c>
     </row>
     <row r="13">
@@ -534,7 +534,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D13">
-        <v>1660000</v>
+        <v>18000000</v>
       </c>
     </row>
     <row r="14">
@@ -548,7 +548,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D14">
-        <v>2075000</v>
+        <v>20000000</v>
       </c>
     </row>
     <row r="15">
@@ -562,7 +562,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D15">
-        <v>4980000</v>
+        <v>41000000</v>
       </c>
     </row>
     <row r="16">
@@ -576,7 +576,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D16">
-        <v>1261600</v>
+        <v>29924015</v>
       </c>
     </row>
     <row r="17">
@@ -590,328 +590,384 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D17">
-        <v>340300</v>
+        <v>8801678.71</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>1500</v>
+        <v>1452</v>
       </c>
       <c r="B18" t="str">
-        <v>Computers and Equipment</v>
+        <v>Due from Aistra Labs AI Software LLC (UAE)</v>
       </c>
       <c r="C18" t="str">
-        <v>Fixed Asset</v>
+        <v>Other Current Asset</v>
       </c>
       <c r="D18">
-        <v>5098075.8</v>
+        <v>6656220.56</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>1510</v>
+        <v>1453</v>
       </c>
       <c r="B19" t="str">
-        <v>Accumulated Depreciation - Computers and Equipment</v>
+        <v>Due from Unconstrained INC</v>
       </c>
       <c r="C19" t="str">
-        <v>Fixed Asset</v>
+        <v>Other Current Asset</v>
       </c>
       <c r="D19">
-        <v>-1885179</v>
+        <v>9693695</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="B20" t="str">
-        <v>Deferred Tax Asset</v>
+        <v>Computers and Equipment</v>
       </c>
       <c r="C20" t="str">
-        <v>Other Asset</v>
+        <v>Fixed Asset</v>
       </c>
       <c r="D20">
-        <v>316661.6</v>
+        <v>37248000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2001</v>
+        <v>1510</v>
       </c>
       <c r="B21" t="str">
-        <v>Accounts Payable</v>
+        <v>Accumulated Depreciation - Computers and Equipment</v>
       </c>
       <c r="C21" t="str">
-        <v>Accounts Payable</v>
+        <v>Fixed Asset</v>
       </c>
       <c r="D21">
-        <v>-2897380.6</v>
+        <v>-13822500</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2100</v>
+        <v>1600</v>
       </c>
       <c r="B22" t="str">
-        <v>Accrued Expenses</v>
+        <v>Deferred Tax Asset</v>
       </c>
       <c r="C22" t="str">
-        <v>Other Current Liability</v>
+        <v>Other Asset</v>
       </c>
       <c r="D22">
-        <v>-1485700</v>
+        <v>2851800</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2150</v>
+        <v>2001</v>
       </c>
       <c r="B23" t="str">
-        <v>Income Tax Payable</v>
+        <v>Accounts Payable</v>
       </c>
       <c r="C23" t="str">
-        <v>Other Current Liability</v>
+        <v>Accounts Payable</v>
       </c>
       <c r="D23">
-        <v>-714513.8</v>
+        <v>-27897200</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="B24" t="str">
-        <v>Provision for Leave Encashment</v>
+        <v>Accrued Expenses</v>
       </c>
       <c r="C24" t="str">
         <v>Other Current Liability</v>
       </c>
       <c r="D24">
-        <v>-573845.4</v>
+        <v>-14860400</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>3001</v>
+        <v>2150</v>
       </c>
       <c r="B25" t="str">
-        <v>Equity Share Capital</v>
+        <v>Income Tax Payable</v>
       </c>
       <c r="C25" t="str">
-        <v>Equity</v>
+        <v>Other Current Liability</v>
       </c>
       <c r="D25">
-        <v>-17517150</v>
+        <v>-6770600</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>3100</v>
+        <v>2200</v>
       </c>
       <c r="B26" t="str">
-        <v>Securities Premium</v>
+        <v>Provision for Leave Encashment</v>
       </c>
       <c r="C26" t="str">
-        <v>Equity</v>
+        <v>Other Current Liability</v>
       </c>
       <c r="D26">
-        <v>-6679840</v>
+        <v>-5247700</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>3200</v>
+        <v>3001</v>
       </c>
       <c r="B27" t="str">
-        <v>Retained Earnings</v>
+        <v>Equity Share Capital</v>
       </c>
       <c r="C27" t="str">
         <v>Equity</v>
       </c>
       <c r="D27">
-        <v>-3431327.9</v>
+        <v>-150000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>4001</v>
+        <v>3100</v>
       </c>
       <c r="B28" t="str">
-        <v>Consulting Revenue</v>
+        <v>Securities Premium</v>
       </c>
       <c r="C28" t="str">
-        <v>Income</v>
+        <v>Equity</v>
       </c>
       <c r="D28">
-        <v>-25216263.2</v>
+        <v>-225000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>4100</v>
+        <v>3200</v>
       </c>
       <c r="B29" t="str">
-        <v>IC Revenue - US</v>
+        <v>Retained Earnings</v>
       </c>
       <c r="C29" t="str">
-        <v>Income</v>
+        <v>Equity</v>
       </c>
       <c r="D29">
-        <v>-3353200</v>
+        <v>-139236584.16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>4101</v>
+        <v>4001</v>
       </c>
       <c r="B30" t="str">
-        <v>IC Revenue - UK</v>
+        <v>Consulting Revenue</v>
       </c>
       <c r="C30" t="str">
         <v>Income</v>
       </c>
       <c r="D30">
-        <v>-854900</v>
+        <v>-138592000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>4500</v>
+        <v>4100</v>
       </c>
       <c r="B31" t="str">
-        <v>Interest Income</v>
+        <v>IC Revenue - US</v>
       </c>
       <c r="C31" t="str">
-        <v>Other Income</v>
+        <v>Income</v>
       </c>
       <c r="D31">
-        <v>-158646.2</v>
+        <v>-12470400</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>5001</v>
+        <v>4101</v>
       </c>
       <c r="B32" t="str">
-        <v>Cost of Services</v>
+        <v>IC Revenue - UK</v>
       </c>
       <c r="C32" t="str">
-        <v>Cost Of Goods Sold</v>
+        <v>Income</v>
       </c>
       <c r="D32">
-        <v>9140740.2</v>
+        <v>-3719731.54</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>6001</v>
+        <v>4102</v>
       </c>
       <c r="B33" t="str">
-        <v>Salaries and Wages</v>
+        <v>IC Revenue - UAE</v>
       </c>
       <c r="C33" t="str">
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="D33">
-        <v>7875820.2</v>
+        <v>-2829680.06</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>6100</v>
+        <v>4103</v>
       </c>
       <c r="B34" t="str">
-        <v>Travel and Conveyance</v>
+        <v>IC Revenue - Unconstrained</v>
       </c>
       <c r="C34" t="str">
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="D34">
-        <v>732591.2</v>
+        <v>-4156800</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>6200</v>
+        <v>4500</v>
       </c>
       <c r="B35" t="str">
-        <v>Professional Fees</v>
+        <v>Interest Income</v>
       </c>
       <c r="C35" t="str">
-        <v>Expense</v>
+        <v>Other Income</v>
       </c>
       <c r="D35">
-        <v>1034346</v>
+        <v>-488000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>6300</v>
+        <v>5001</v>
       </c>
       <c r="B36" t="str">
-        <v>Software Subscriptions</v>
+        <v>Cost of Services</v>
       </c>
       <c r="C36" t="str">
-        <v>Expense</v>
+        <v>Cost Of Goods Sold</v>
       </c>
       <c r="D36">
-        <v>805100</v>
+        <v>46640000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>6400</v>
+        <v>6001</v>
       </c>
       <c r="B37" t="str">
-        <v>Rent</v>
+        <v>Salaries and Wages</v>
       </c>
       <c r="C37" t="str">
         <v>Expense</v>
       </c>
       <c r="D37">
-        <v>1322339.4</v>
+        <v>73960000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>6500</v>
+        <v>6100</v>
       </c>
       <c r="B38" t="str">
-        <v>Depreciation</v>
+        <v>Travel and Conveyance</v>
       </c>
       <c r="C38" t="str">
         <v>Expense</v>
       </c>
       <c r="D38">
-        <v>441659.6</v>
+        <v>3896000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>6900</v>
+        <v>6200</v>
       </c>
       <c r="B39" t="str">
-        <v>Income Tax Expense</v>
+        <v>Professional Fees</v>
       </c>
       <c r="C39" t="str">
         <v>Expense</v>
       </c>
       <c r="D39">
-        <v>967614</v>
+        <v>5544000</v>
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="str">
+        <v>6300</v>
+      </c>
       <c r="B40" t="str">
+        <v>Software Subscriptions</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D40">
+        <v>4208000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>6400</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Rent</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D41">
+        <v>6280000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>6500</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Depreciation</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D42">
+        <v>2272000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>6900</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Income Tax Expense</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D43">
+        <v>4968000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="str">
         <v>Total</v>
       </c>
-      <c r="D40">
+      <c r="D44">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D40"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D44"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/Trial_Balance_IN_Jul-26.xlsx
+++ b/samples/Trial_Balance_IN_Jul-26.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D53"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>261463736.49</v>
+        <v>238004584.16</v>
       </c>
     </row>
     <row r="8">
@@ -464,7 +464,7 @@
         <v>Cash</v>
       </c>
       <c r="D8">
-        <v>82450</v>
+        <v>82000</v>
       </c>
     </row>
     <row r="9">
@@ -478,7 +478,7 @@
         <v>Accounts Receivable</v>
       </c>
       <c r="D9">
-        <v>138370500</v>
+        <v>138900000</v>
       </c>
     </row>
     <row r="10">
@@ -486,13 +486,13 @@
         <v>1200</v>
       </c>
       <c r="B10" t="str">
-        <v>Prepaid Expenses</v>
+        <v>Security Deposit</v>
       </c>
       <c r="C10" t="str">
-        <v>Other Current Asset</v>
+        <v>Other Asset</v>
       </c>
       <c r="D10">
-        <v>6227400</v>
+        <v>12350000</v>
       </c>
     </row>
     <row r="11">
@@ -506,468 +506,594 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D11">
-        <v>5024600</v>
+        <v>4960000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1300</v>
+        <v>1260</v>
       </c>
       <c r="B12" t="str">
-        <v>Security Deposit</v>
+        <v>TDS Receivable</v>
       </c>
       <c r="C12" t="str">
-        <v>Other Asset</v>
+        <v>Other Current Asset</v>
       </c>
       <c r="D12">
-        <v>11979500</v>
+        <v>3180000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="B13" t="str">
-        <v>Investment - Aistra Labs AI Software LLC (UAE)</v>
+        <v>Prepaid Expenses</v>
       </c>
       <c r="C13" t="str">
-        <v>Other Asset</v>
+        <v>Other Current Asset</v>
       </c>
       <c r="D13">
-        <v>18000000</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="B14" t="str">
-        <v>Investment - Aistra Labs UK Ltd</v>
+        <v>Investment - Aistra Labs AI Software LLC (UAE)</v>
       </c>
       <c r="C14" t="str">
         <v>Other Asset</v>
       </c>
       <c r="D14">
-        <v>20000000</v>
+        <v>18000000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="B15" t="str">
-        <v>Investment - Unconstrained INC</v>
+        <v>Investment - Aistra Labs UK Ltd</v>
       </c>
       <c r="C15" t="str">
         <v>Other Asset</v>
       </c>
       <c r="D15">
-        <v>41000000</v>
+        <v>20000000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>1450</v>
+        <v>1402</v>
       </c>
       <c r="B16" t="str">
-        <v>Due from Aistra Labs Inc (US)</v>
+        <v>Investment - Unconstrained INC</v>
       </c>
       <c r="C16" t="str">
-        <v>Other Current Asset</v>
+        <v>Other Asset</v>
       </c>
       <c r="D16">
-        <v>29924015</v>
+        <v>41000000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="B17" t="str">
-        <v>Due from Aistra Labs UK Ltd</v>
+        <v>Due from Aistra Labs Inc (US)</v>
       </c>
       <c r="C17" t="str">
         <v>Other Current Asset</v>
       </c>
       <c r="D17">
-        <v>8801678.71</v>
+        <v>29800000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="B18" t="str">
-        <v>Due from Aistra Labs AI Software LLC (UAE)</v>
+        <v>Due from Aistra Labs UK Ltd</v>
       </c>
       <c r="C18" t="str">
         <v>Other Current Asset</v>
       </c>
       <c r="D18">
-        <v>6656220.56</v>
+        <v>8700000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="B19" t="str">
-        <v>Due from Unconstrained INC</v>
+        <v>Due from Aistra Labs AI Software LLC (UAE)</v>
       </c>
       <c r="C19" t="str">
         <v>Other Current Asset</v>
       </c>
       <c r="D19">
-        <v>9693695</v>
+        <v>6500000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>1500</v>
+        <v>1453</v>
       </c>
       <c r="B20" t="str">
-        <v>Computers and Equipment</v>
+        <v>Due from Unconstrained INC</v>
       </c>
       <c r="C20" t="str">
-        <v>Fixed Asset</v>
+        <v>Other Current Asset</v>
       </c>
       <c r="D20">
-        <v>37248000</v>
+        <v>9600000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="B21" t="str">
-        <v>Accumulated Depreciation - Computers and Equipment</v>
+        <v>Computers and Equipment</v>
       </c>
       <c r="C21" t="str">
         <v>Fixed Asset</v>
       </c>
       <c r="D21">
-        <v>-13822500</v>
+        <v>38400000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>1600</v>
+        <v>1510</v>
       </c>
       <c r="B22" t="str">
-        <v>Deferred Tax Asset</v>
+        <v>Accumulated Depreciation - Computers and Equipment</v>
       </c>
       <c r="C22" t="str">
-        <v>Other Asset</v>
+        <v>Fixed Asset</v>
       </c>
       <c r="D22">
-        <v>2851800</v>
+        <v>-13700000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2001</v>
+        <v>1520</v>
       </c>
       <c r="B23" t="str">
-        <v>Accounts Payable</v>
+        <v>Furniture and Fixtures</v>
       </c>
       <c r="C23" t="str">
-        <v>Accounts Payable</v>
+        <v>Fixed Asset</v>
       </c>
       <c r="D23">
-        <v>-27897200</v>
+        <v>6500000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2100</v>
+        <v>1530</v>
       </c>
       <c r="B24" t="str">
-        <v>Accrued Expenses</v>
+        <v>Accumulated Depreciation - Furniture and Fixtures</v>
       </c>
       <c r="C24" t="str">
-        <v>Other Current Liability</v>
+        <v>Fixed Asset</v>
       </c>
       <c r="D24">
-        <v>-14860400</v>
+        <v>-1780000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2150</v>
+        <v>1600</v>
       </c>
       <c r="B25" t="str">
-        <v>Income Tax Payable</v>
+        <v>Deferred Tax Asset</v>
       </c>
       <c r="C25" t="str">
-        <v>Other Current Liability</v>
+        <v>Other Asset</v>
       </c>
       <c r="D25">
-        <v>-6770600</v>
+        <v>2940000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2200</v>
+        <v>2001</v>
       </c>
       <c r="B26" t="str">
-        <v>Provision for Leave Encashment</v>
+        <v>Accounts Payable</v>
       </c>
       <c r="C26" t="str">
-        <v>Other Current Liability</v>
+        <v>Accounts Payable</v>
       </c>
       <c r="D26">
-        <v>-5247700</v>
+        <v>-196230000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>3001</v>
+        <v>2100</v>
       </c>
       <c r="B27" t="str">
-        <v>Equity Share Capital</v>
+        <v>Accrued Expenses</v>
       </c>
       <c r="C27" t="str">
-        <v>Equity</v>
+        <v>Other Current Liability</v>
       </c>
       <c r="D27">
-        <v>-150000000</v>
+        <v>-14900000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>3100</v>
+        <v>2150</v>
       </c>
       <c r="B28" t="str">
-        <v>Securities Premium</v>
+        <v>Income Tax Payable</v>
       </c>
       <c r="C28" t="str">
-        <v>Equity</v>
+        <v>Other Current Liability</v>
       </c>
       <c r="D28">
-        <v>-225000000</v>
+        <v>-6200000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>3200</v>
+        <v>2200</v>
       </c>
       <c r="B29" t="str">
-        <v>Retained Earnings</v>
+        <v>Provision for Leave Encashment</v>
       </c>
       <c r="C29" t="str">
-        <v>Equity</v>
+        <v>Other Current Liability</v>
       </c>
       <c r="D29">
-        <v>-139236584.16</v>
+        <v>-5300000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>4001</v>
+        <v>2210</v>
       </c>
       <c r="B30" t="str">
-        <v>Consulting Revenue</v>
+        <v>Provision for Gratuity</v>
       </c>
       <c r="C30" t="str">
-        <v>Income</v>
+        <v>Other Current Liability</v>
       </c>
       <c r="D30">
-        <v>-138592000</v>
+        <v>-8600000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>4100</v>
+        <v>2300</v>
       </c>
       <c r="B31" t="str">
-        <v>IC Revenue - US</v>
+        <v>TDS Payable</v>
       </c>
       <c r="C31" t="str">
-        <v>Income</v>
+        <v>Other Current Liability</v>
       </c>
       <c r="D31">
-        <v>-12470400</v>
+        <v>-2050000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>4101</v>
+        <v>3001</v>
       </c>
       <c r="B32" t="str">
-        <v>IC Revenue - UK</v>
+        <v>Equity Share Capital</v>
       </c>
       <c r="C32" t="str">
-        <v>Income</v>
+        <v>Equity</v>
       </c>
       <c r="D32">
-        <v>-3719731.54</v>
+        <v>-100000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>4102</v>
+        <v>3100</v>
       </c>
       <c r="B33" t="str">
-        <v>IC Revenue - UAE</v>
+        <v>Securities Premium</v>
       </c>
       <c r="C33" t="str">
-        <v>Income</v>
+        <v>Equity</v>
       </c>
       <c r="D33">
-        <v>-2829680.06</v>
+        <v>-50000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>4103</v>
+        <v>3200</v>
       </c>
       <c r="B34" t="str">
-        <v>IC Revenue - Unconstrained</v>
+        <v>Retained Earnings</v>
       </c>
       <c r="C34" t="str">
-        <v>Income</v>
+        <v>Equity</v>
       </c>
       <c r="D34">
-        <v>-4156800</v>
+        <v>-165000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>4500</v>
+        <v>4001</v>
       </c>
       <c r="B35" t="str">
-        <v>Interest Income</v>
+        <v>Consulting Revenue</v>
       </c>
       <c r="C35" t="str">
-        <v>Other Income</v>
+        <v>Income</v>
       </c>
       <c r="D35">
-        <v>-488000</v>
+        <v>-176666584.16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>5001</v>
+        <v>4100</v>
       </c>
       <c r="B36" t="str">
-        <v>Cost of Services</v>
+        <v>IC Revenue - US</v>
       </c>
       <c r="C36" t="str">
-        <v>Cost Of Goods Sold</v>
+        <v>Income</v>
       </c>
       <c r="D36">
-        <v>46640000</v>
+        <v>-15100000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>6001</v>
+        <v>4101</v>
       </c>
       <c r="B37" t="str">
-        <v>Salaries and Wages</v>
+        <v>IC Revenue - UK</v>
       </c>
       <c r="C37" t="str">
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="D37">
-        <v>73960000</v>
+        <v>-4500000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>6100</v>
+        <v>4102</v>
       </c>
       <c r="B38" t="str">
-        <v>Travel and Conveyance</v>
+        <v>IC Revenue - UAE</v>
       </c>
       <c r="C38" t="str">
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="D38">
-        <v>3896000</v>
+        <v>-3400000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>6200</v>
+        <v>4103</v>
       </c>
       <c r="B39" t="str">
-        <v>Professional Fees</v>
+        <v>IC Revenue - Unconstrained</v>
       </c>
       <c r="C39" t="str">
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="D39">
-        <v>5544000</v>
+        <v>-5050000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>6300</v>
+        <v>4500</v>
       </c>
       <c r="B40" t="str">
-        <v>Software Subscriptions</v>
+        <v>Interest Income</v>
       </c>
       <c r="C40" t="str">
-        <v>Expense</v>
+        <v>Other Income</v>
       </c>
       <c r="D40">
-        <v>4208000</v>
+        <v>-580000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>6400</v>
+        <v>5001</v>
       </c>
       <c r="B41" t="str">
-        <v>Rent</v>
+        <v>Cost of Services</v>
       </c>
       <c r="C41" t="str">
-        <v>Expense</v>
+        <v>Cost Of Goods Sold</v>
       </c>
       <c r="D41">
-        <v>6280000</v>
+        <v>56900000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>6500</v>
+        <v>6001</v>
       </c>
       <c r="B42" t="str">
-        <v>Depreciation</v>
+        <v>Salaries and Wages</v>
       </c>
       <c r="C42" t="str">
         <v>Expense</v>
       </c>
       <c r="D42">
-        <v>2272000</v>
+        <v>91800000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>6900</v>
+        <v>6010</v>
       </c>
       <c r="B43" t="str">
-        <v>Income Tax Expense</v>
+        <v>Contribution to Provident Fund</v>
       </c>
       <c r="C43" t="str">
         <v>Expense</v>
       </c>
       <c r="D43">
-        <v>4968000</v>
+        <v>5500000</v>
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="str">
+        <v>6100</v>
+      </c>
       <c r="B44" t="str">
+        <v>Travel and Conveyance</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D44">
+        <v>4650000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>6200</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Professional Fees</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D45">
+        <v>6700000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>6210</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Audit Fees</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D46">
+        <v>850000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>6300</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Software Subscriptions</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D47">
+        <v>5180000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>6400</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Office Expenses</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D48">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>6410</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Rent</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D49">
+        <v>7850000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>6500</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Depreciation</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D50">
+        <v>2770000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>6900</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Income Tax Expense</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D51">
+        <v>5900000</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>6910</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Deferred Tax Expense</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D52">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="str">
         <v>Total</v>
       </c>
-      <c r="D44">
+      <c r="D53">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D44"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D53"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/Trial_Balance_IN_Jul-26.xlsx
+++ b/samples/Trial_Balance_IN_Jul-26.xlsx
@@ -441,21 +441,21 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>1001</v>
+        <v>1010</v>
       </c>
       <c r="B7" t="str">
-        <v>HDFC Bank Current Account</v>
+        <v>Operating Bank</v>
       </c>
       <c r="C7" t="str">
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>238004584.16</v>
+        <v>348074584.16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="B8" t="str">
         <v>Petty Cash</v>
@@ -478,7 +478,7 @@
         <v>Accounts Receivable</v>
       </c>
       <c r="D9">
-        <v>138900000</v>
+        <v>190000000</v>
       </c>
     </row>
     <row r="10">
@@ -520,147 +520,147 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D12">
-        <v>3180000</v>
+        <v>3179999.95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1300</v>
+        <v>1270</v>
       </c>
       <c r="B13" t="str">
-        <v>Prepaid Expenses</v>
+        <v>GST Input Credit</v>
       </c>
       <c r="C13" t="str">
         <v>Other Current Asset</v>
       </c>
       <c r="D13">
-        <v>1200000</v>
+        <v>1850000.05</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="B14" t="str">
-        <v>Investment - Aistra Labs AI Software LLC (UAE)</v>
+        <v>Prepaid Expenses</v>
       </c>
       <c r="C14" t="str">
-        <v>Other Asset</v>
+        <v>Other Current Asset</v>
       </c>
       <c r="D14">
-        <v>18000000</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="B15" t="str">
-        <v>Investment - Aistra Labs UK Ltd</v>
+        <v>Investment - Aistra Labs AI Software LLC (UAE)</v>
       </c>
       <c r="C15" t="str">
         <v>Other Asset</v>
       </c>
       <c r="D15">
-        <v>20000000</v>
+        <v>18000000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="B16" t="str">
-        <v>Investment - Unconstrained INC</v>
+        <v>Investment - Aistra Labs UK Ltd</v>
       </c>
       <c r="C16" t="str">
         <v>Other Asset</v>
       </c>
       <c r="D16">
-        <v>41000000</v>
+        <v>20000000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>1450</v>
+        <v>1402</v>
       </c>
       <c r="B17" t="str">
-        <v>Due from Aistra Labs Inc (US)</v>
+        <v>Investment - Unconstrained INC</v>
       </c>
       <c r="C17" t="str">
-        <v>Other Current Asset</v>
+        <v>Other Asset</v>
       </c>
       <c r="D17">
-        <v>29800000</v>
+        <v>41000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="B18" t="str">
-        <v>Due from Aistra Labs UK Ltd</v>
+        <v>Due from Aistra Labs Inc (US)</v>
       </c>
       <c r="C18" t="str">
         <v>Other Current Asset</v>
       </c>
       <c r="D18">
-        <v>8700000</v>
+        <v>29800000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="B19" t="str">
-        <v>Due from Aistra Labs AI Software LLC (UAE)</v>
+        <v>Due from Aistra Labs UK Ltd</v>
       </c>
       <c r="C19" t="str">
         <v>Other Current Asset</v>
       </c>
       <c r="D19">
-        <v>6500000</v>
+        <v>8700000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="B20" t="str">
-        <v>Due from Unconstrained INC</v>
+        <v>Due from Aistra Labs AI Software LLC (UAE)</v>
       </c>
       <c r="C20" t="str">
         <v>Other Current Asset</v>
       </c>
       <c r="D20">
-        <v>9600000</v>
+        <v>6500000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>1500</v>
+        <v>1453</v>
       </c>
       <c r="B21" t="str">
-        <v>Computers and Equipment</v>
+        <v>Due from Unconstrained INC</v>
       </c>
       <c r="C21" t="str">
-        <v>Fixed Asset</v>
+        <v>Other Current Asset</v>
       </c>
       <c r="D21">
-        <v>38400000</v>
+        <v>9600000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="B22" t="str">
-        <v>Accumulated Depreciation - Computers and Equipment</v>
+        <v>Computers and Equipment (net)</v>
       </c>
       <c r="C22" t="str">
         <v>Fixed Asset</v>
       </c>
       <c r="D22">
-        <v>-13700000</v>
+        <v>24600000</v>
       </c>
     </row>
     <row r="23">
@@ -668,293 +668,293 @@
         <v>1520</v>
       </c>
       <c r="B23" t="str">
-        <v>Furniture and Fixtures</v>
+        <v>Furniture and Fixtures (net)</v>
       </c>
       <c r="C23" t="str">
         <v>Fixed Asset</v>
       </c>
       <c r="D23">
-        <v>6500000</v>
+        <v>4720000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>1530</v>
+        <v>1600</v>
       </c>
       <c r="B24" t="str">
-        <v>Accumulated Depreciation - Furniture and Fixtures</v>
+        <v>Deferred Tax Asset</v>
       </c>
       <c r="C24" t="str">
-        <v>Fixed Asset</v>
+        <v>Other Asset</v>
       </c>
       <c r="D24">
-        <v>-1780000</v>
+        <v>2940000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>1600</v>
+        <v>2001</v>
       </c>
       <c r="B25" t="str">
-        <v>Deferred Tax Asset</v>
+        <v>Accounts Payable</v>
       </c>
       <c r="C25" t="str">
-        <v>Other Asset</v>
+        <v>Accounts Payable</v>
       </c>
       <c r="D25">
-        <v>2940000</v>
+        <v>-19250000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2001</v>
+        <v>2100</v>
       </c>
       <c r="B26" t="str">
-        <v>Accounts Payable</v>
+        <v>Accrued Expenses</v>
       </c>
       <c r="C26" t="str">
-        <v>Accounts Payable</v>
+        <v>Other Current Liability</v>
       </c>
       <c r="D26">
-        <v>-196230000</v>
+        <v>-9500000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2100</v>
+        <v>2150</v>
       </c>
       <c r="B27" t="str">
-        <v>Accrued Expenses</v>
+        <v>Income Tax Payable</v>
       </c>
       <c r="C27" t="str">
         <v>Other Current Liability</v>
       </c>
       <c r="D27">
-        <v>-14900000</v>
+        <v>-6199999.63</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2150</v>
+        <v>2200</v>
       </c>
       <c r="B28" t="str">
-        <v>Income Tax Payable</v>
+        <v>Provision for Leave Encashment</v>
       </c>
       <c r="C28" t="str">
         <v>Other Current Liability</v>
       </c>
       <c r="D28">
-        <v>-6200000</v>
+        <v>-3300000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2200</v>
+        <v>2210</v>
       </c>
       <c r="B29" t="str">
-        <v>Provision for Leave Encashment</v>
+        <v>Provision for Gratuity</v>
       </c>
       <c r="C29" t="str">
         <v>Other Current Liability</v>
       </c>
       <c r="D29">
-        <v>-5300000</v>
+        <v>-5800000.37</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2210</v>
+        <v>2300</v>
       </c>
       <c r="B30" t="str">
-        <v>Provision for Gratuity</v>
+        <v>TDS Payable</v>
       </c>
       <c r="C30" t="str">
         <v>Other Current Liability</v>
       </c>
       <c r="D30">
-        <v>-8600000</v>
+        <v>-2150000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2300</v>
+        <v>3001</v>
       </c>
       <c r="B31" t="str">
-        <v>TDS Payable</v>
+        <v>Equity Share Capital</v>
       </c>
       <c r="C31" t="str">
-        <v>Other Current Liability</v>
+        <v>Equity</v>
       </c>
       <c r="D31">
-        <v>-2050000</v>
+        <v>-100000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>3001</v>
+        <v>3100</v>
       </c>
       <c r="B32" t="str">
-        <v>Equity Share Capital</v>
+        <v>Securities Premium</v>
       </c>
       <c r="C32" t="str">
         <v>Equity</v>
       </c>
       <c r="D32">
-        <v>-100000000</v>
+        <v>-400000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="B33" t="str">
-        <v>Securities Premium</v>
+        <v>Retained Earnings</v>
       </c>
       <c r="C33" t="str">
         <v>Equity</v>
       </c>
       <c r="D33">
-        <v>-50000000</v>
+        <v>-165000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>3200</v>
+        <v>4000</v>
       </c>
       <c r="B34" t="str">
-        <v>Retained Earnings</v>
+        <v>Sales</v>
       </c>
       <c r="C34" t="str">
-        <v>Equity</v>
+        <v>Income</v>
       </c>
       <c r="D34">
-        <v>-165000000</v>
+        <v>-29466584.16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>4001</v>
+        <v>4100</v>
       </c>
       <c r="B35" t="str">
-        <v>Consulting Revenue</v>
+        <v>IC Revenue - US</v>
       </c>
       <c r="C35" t="str">
         <v>Income</v>
       </c>
       <c r="D35">
-        <v>-176666584.16</v>
+        <v>-15100000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>4100</v>
+        <v>4101</v>
       </c>
       <c r="B36" t="str">
-        <v>IC Revenue - US</v>
+        <v>IC Revenue - UK</v>
       </c>
       <c r="C36" t="str">
         <v>Income</v>
       </c>
       <c r="D36">
-        <v>-15100000</v>
+        <v>-4500000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>4101</v>
+        <v>4102</v>
       </c>
       <c r="B37" t="str">
-        <v>IC Revenue - UK</v>
+        <v>IC Revenue - UAE</v>
       </c>
       <c r="C37" t="str">
         <v>Income</v>
       </c>
       <c r="D37">
-        <v>-4500000</v>
+        <v>-3400000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>4102</v>
+        <v>4103</v>
       </c>
       <c r="B38" t="str">
-        <v>IC Revenue - UAE</v>
+        <v>IC Revenue - Unconstrained</v>
       </c>
       <c r="C38" t="str">
         <v>Income</v>
       </c>
       <c r="D38">
-        <v>-3400000</v>
+        <v>-5050000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>4103</v>
+        <v>4500</v>
       </c>
       <c r="B39" t="str">
-        <v>IC Revenue - Unconstrained</v>
+        <v>Interest Income</v>
       </c>
       <c r="C39" t="str">
-        <v>Income</v>
+        <v>Other Income</v>
       </c>
       <c r="D39">
-        <v>-5050000</v>
+        <v>-340000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>4500</v>
+        <v>5001</v>
       </c>
       <c r="B40" t="str">
-        <v>Interest Income</v>
+        <v>Cost of Services</v>
       </c>
       <c r="C40" t="str">
-        <v>Other Income</v>
+        <v>Cost Of Goods Sold</v>
       </c>
       <c r="D40">
-        <v>-580000</v>
+        <v>11700000.22</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>5001</v>
+        <v>6001</v>
       </c>
       <c r="B41" t="str">
-        <v>Cost of Services</v>
+        <v>Salaries and Wages</v>
       </c>
       <c r="C41" t="str">
-        <v>Cost Of Goods Sold</v>
+        <v>Expense</v>
       </c>
       <c r="D41">
-        <v>56900000</v>
+        <v>18009999.78</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>6001</v>
+        <v>6010</v>
       </c>
       <c r="B42" t="str">
-        <v>Salaries and Wages</v>
+        <v>Contribution to Provident Fund</v>
       </c>
       <c r="C42" t="str">
         <v>Expense</v>
       </c>
       <c r="D42">
-        <v>91800000</v>
+        <v>1090000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>6010</v>
+        <v>6020</v>
       </c>
       <c r="B43" t="str">
-        <v>Contribution to Provident Fund</v>
+        <v>Gratuity Expense</v>
       </c>
       <c r="C43" t="str">
         <v>Expense</v>
       </c>
       <c r="D43">
-        <v>5500000</v>
+        <v>290000</v>
       </c>
     </row>
     <row r="44">
@@ -968,7 +968,7 @@
         <v>Expense</v>
       </c>
       <c r="D44">
-        <v>4650000</v>
+        <v>920000</v>
       </c>
     </row>
     <row r="45">
@@ -982,7 +982,7 @@
         <v>Expense</v>
       </c>
       <c r="D45">
-        <v>6700000</v>
+        <v>1350000</v>
       </c>
     </row>
     <row r="46">
@@ -996,7 +996,7 @@
         <v>Expense</v>
       </c>
       <c r="D46">
-        <v>850000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="47">
@@ -1010,7 +1010,7 @@
         <v>Expense</v>
       </c>
       <c r="D47">
-        <v>5180000</v>
+        <v>1040000</v>
       </c>
     </row>
     <row r="48">
@@ -1038,7 +1038,7 @@
         <v>Expense</v>
       </c>
       <c r="D49">
-        <v>7850000</v>
+        <v>1600000</v>
       </c>
     </row>
     <row r="50">
@@ -1052,7 +1052,7 @@
         <v>Expense</v>
       </c>
       <c r="D50">
-        <v>2770000</v>
+        <v>570000</v>
       </c>
     </row>
     <row r="51">
@@ -1066,7 +1066,7 @@
         <v>Expense</v>
       </c>
       <c r="D51">
-        <v>5900000</v>
+        <v>3910000</v>
       </c>
     </row>
     <row r="52">

--- a/samples/Trial_Balance_IN_Jul-26.xlsx
+++ b/samples/Trial_Balance_IN_Jul-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>348074584.16</v>
+        <v>510074584.37</v>
       </c>
     </row>
     <row r="8">
@@ -478,7 +478,7 @@
         <v>Accounts Receivable</v>
       </c>
       <c r="D9">
-        <v>190000000</v>
+        <v>28000000</v>
       </c>
     </row>
     <row r="10">
@@ -506,7 +506,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D11">
-        <v>4960000</v>
+        <v>4959999.79</v>
       </c>
     </row>
     <row r="12">
@@ -520,7 +520,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D12">
-        <v>3179999.95</v>
+        <v>3180000</v>
       </c>
     </row>
     <row r="13">
@@ -534,7 +534,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D13">
-        <v>1850000.05</v>
+        <v>1850000</v>
       </c>
     </row>
     <row r="14">
@@ -828,7 +828,7 @@
         <v>Income</v>
       </c>
       <c r="D34">
-        <v>-29466584.16</v>
+        <v>-29456584.09</v>
       </c>
     </row>
     <row r="35">
@@ -884,7 +884,7 @@
         <v>Income</v>
       </c>
       <c r="D38">
-        <v>-5050000</v>
+        <v>-5050000.07</v>
       </c>
     </row>
     <row r="39">
@@ -898,7 +898,7 @@
         <v>Other Income</v>
       </c>
       <c r="D39">
-        <v>-340000</v>
+        <v>-250000</v>
       </c>
     </row>
     <row r="40">
@@ -912,7 +912,7 @@
         <v>Cost Of Goods Sold</v>
       </c>
       <c r="D40">
-        <v>11700000.22</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="41">
@@ -926,7 +926,7 @@
         <v>Expense</v>
       </c>
       <c r="D41">
-        <v>18009999.78</v>
+        <v>29250000.06</v>
       </c>
     </row>
     <row r="42">
@@ -940,7 +940,7 @@
         <v>Expense</v>
       </c>
       <c r="D42">
-        <v>1090000</v>
+        <v>2419999.94</v>
       </c>
     </row>
     <row r="43">
@@ -954,7 +954,7 @@
         <v>Expense</v>
       </c>
       <c r="D43">
-        <v>290000</v>
+        <v>430000</v>
       </c>
     </row>
     <row r="44">
@@ -1052,7 +1052,7 @@
         <v>Expense</v>
       </c>
       <c r="D50">
-        <v>570000</v>
+        <v>1400000</v>
       </c>
     </row>
     <row r="51">
@@ -1066,7 +1066,7 @@
         <v>Expense</v>
       </c>
       <c r="D51">
-        <v>3910000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="52">
@@ -1080,7 +1080,7 @@
         <v>Expense</v>
       </c>
       <c r="D52">
-        <v>140000</v>
+        <v>-100000</v>
       </c>
     </row>
     <row r="53">

--- a/samples/Trial_Balance_IN_Jul-26.xlsx
+++ b/samples/Trial_Balance_IN_Jul-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>510074584.37</v>
+        <v>510074584.16</v>
       </c>
     </row>
     <row r="8">
@@ -506,7 +506,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D11">
-        <v>4959999.79</v>
+        <v>4960000</v>
       </c>
     </row>
     <row r="12">
@@ -730,7 +730,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D27">
-        <v>-6199999.63</v>
+        <v>-6200000</v>
       </c>
     </row>
     <row r="28">
@@ -758,7 +758,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D29">
-        <v>-5800000.37</v>
+        <v>-5800000</v>
       </c>
     </row>
     <row r="30">
@@ -828,7 +828,7 @@
         <v>Income</v>
       </c>
       <c r="D34">
-        <v>-29456584.09</v>
+        <v>-29456584.16</v>
       </c>
     </row>
     <row r="35">
@@ -884,7 +884,7 @@
         <v>Income</v>
       </c>
       <c r="D38">
-        <v>-5050000.07</v>
+        <v>-5050000</v>
       </c>
     </row>
     <row r="39">
@@ -926,7 +926,7 @@
         <v>Expense</v>
       </c>
       <c r="D41">
-        <v>29250000.06</v>
+        <v>29250000</v>
       </c>
     </row>
     <row r="42">
@@ -940,7 +940,7 @@
         <v>Expense</v>
       </c>
       <c r="D42">
-        <v>2419999.94</v>
+        <v>2420000</v>
       </c>
     </row>
     <row r="43">
@@ -1066,7 +1066,7 @@
         <v>Expense</v>
       </c>
       <c r="D51">
-        <v>2000000</v>
+        <v>1750000</v>
       </c>
     </row>
     <row r="52">
@@ -1080,7 +1080,7 @@
         <v>Expense</v>
       </c>
       <c r="D52">
-        <v>-100000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="53">
